--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.06447612477368</v>
+        <v>5.697977370275724</v>
       </c>
       <c r="D2" t="n">
-        <v>28.28109054119991</v>
+        <v>4.595677212944985</v>
       </c>
       <c r="E2" t="n">
-        <v>7.608144022431319</v>
+        <v>1.236323403645089</v>
       </c>
       <c r="F2" t="n">
-        <v>7.785479329886249</v>
+        <v>1.265140391106516</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.34953600244867</v>
+        <v>4.119299600397909</v>
       </c>
       <c r="D3" t="n">
-        <v>25.50003350343424</v>
+        <v>4.143755444308065</v>
       </c>
       <c r="E3" t="n">
-        <v>7.608144022431319</v>
+        <v>1.236323403645089</v>
       </c>
       <c r="F3" t="n">
-        <v>7.785479329886249</v>
+        <v>1.265140391106516</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.81018840792572</v>
+        <v>7.44415561628793</v>
       </c>
       <c r="D4" t="n">
-        <v>44.17662765726059</v>
+        <v>7.178701994304846</v>
       </c>
       <c r="E4" t="n">
-        <v>7.608144022431319</v>
+        <v>1.236323403645089</v>
       </c>
       <c r="F4" t="n">
-        <v>7.785479329886249</v>
+        <v>1.265140391106516</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.82891444922387</v>
+        <v>6.634698597998878</v>
       </c>
       <c r="D5" t="n">
-        <v>25.40622962613454</v>
+        <v>4.128512314246863</v>
       </c>
       <c r="E5" t="n">
-        <v>7.608144022431319</v>
+        <v>1.236323403645089</v>
       </c>
       <c r="F5" t="n">
-        <v>7.785479329886249</v>
+        <v>1.265140391106516</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
